--- a/02_加值成品/生物/生物8-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-2 生態系與能量流動　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物8-2 生態系與能量流動　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>自製養分的生物是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>生產者</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>食物鏈</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>分解者</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>植物</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>攝食他物的生物是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>生產者</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>消費者</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>逐級遞減</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>動物</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>分解遺體的生物是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>逐級遞減</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>食物鏈</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>生產者</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>分解者</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>細菌真菌</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>能量的最終來源是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>太陽</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>食物鏈</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>高階消費者</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>非生物環境</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>陽光</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>能量沿什麼流動？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>物質無法循環</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>食物鏈</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>逐級遞減</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>鏈</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>能量隨營養階層？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>逐級遞減</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>循環</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>食物網</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>遞減</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>物質能循環利用嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>逐級遞減</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>能</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>非生物環境</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>多條食物鏈交織成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>物質無法循環</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>食物網</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>高階消費者</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>分解者</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>網</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>植物在生態系扮演的角色是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>逐級遞減</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>越少</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>生產者</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>生產者</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>動物多屬於生態系的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>物質無法循環</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>食物鏈</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>消費者</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>循環</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>消費者</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-2 生態系與能量流動　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物8-2 生態系與能量流動　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>食物鏈箭頭指向？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>單向</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>越少</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>取食者</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>能量流向</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>越高階消費者能量？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>循環</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>取食者</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>越少</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>遞減</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>分解者的作用是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>能量以熱散失無法回收,物質可被分解再利用</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>大部分流失僅少部分傳遞</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>能量持續輸入物質循環維持運作</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>分解遺體回歸物質</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>生態系包含生物與？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>分解者</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>高階消費者</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>取食者</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>非生物環境</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>草→兔→鷹中鷹是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>生產者</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>取食者</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>分解者</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>高階消費者</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>頂端</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>能量流動是單向還循環？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>單向</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>逐級遞減</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>食物網</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>不循環</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>碳可以在生態系中？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>物質無法循環</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>食物鏈</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>物質循環</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>生產者透過什麼獲得能量？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>生產者</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>光合作用</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>分解者</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>物質無法循環</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>製養</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>能量在食物鏈每一級大多如何？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大部分流失僅少部分傳遞</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>太陽經生產者沿食物鏈逐級傳遞且每級遞減</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>把遺體分解使養分回歸供生產者利用</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>能量以熱散失無法回收,物質可被分解再利用</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>遞減</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>缺少分解者生態系會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>物質無法循環</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>生產者</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>消費者</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-2 生態系與能量流動　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物8-2 生態系與能量流動　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明能量在生態系如何流動與遞減？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>分解遺體回歸物質</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>太陽經生產者沿食物鏈逐級傳遞且每級遞減</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>多條交織更貼近真實複雜關係</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>越高階可用能量越少</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>流動</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何能量單向流動而物質可循環？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>牽動相關物種數量破壞平衡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>能量持續輸入物質循環維持運作</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>能量以熱散失無法回收,物質可被分解再利用</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>生產者固碳分解者釋碳回環境</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>分解者在物質循環的關鍵角色？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>多條交織更貼近真實複雜關係</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>太陽經生產者沿食物鏈逐級傳遞且每級遞減</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>能量持續輸入物質循環維持運作</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>把遺體分解使養分回歸供生產者利用</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>關鍵</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>食物網比食物鏈更能反映生態的原因？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>分解遺體回歸物質</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>把遺體分解使養分回歸供生產者利用</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>多條交織更貼近真實複雜關係</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>太陽經生產者沿食物鏈逐級傳遞且每級遞減</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>食物網</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>若某環節生物大量減少對食物網影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>能量持續輸入物質循環維持運作</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>太陽經生產者沿食物鏈逐級傳遞且每級遞減</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>能量來源減少各階層受衝擊</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>牽動相關物種數量破壞平衡</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>連鎖</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>能量塔為何呈上小下大？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>太陽經生產者沿食物鏈逐級傳遞且每級遞減</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>多條交織更貼近真實複雜關係</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>牽動相關物種數量破壞平衡</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>越高階可用能量越少</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>能量塔</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>碳循環中生產者與分解者角色？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>生產者固碳分解者釋碳回環境</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>能量來源減少各階層受衝擊</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>能量以熱散失無法回收,物質可被分解再利用</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>多條交織更貼近真實複雜關係</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>碳循環</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>生態系穩定與物質能量的關係？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>能量持續輸入物質循環維持運作</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>能量以熱散失無法回收,物質可被分解再利用</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>多條交織更貼近真實複雜關係</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>能量來源減少各階層受衝擊</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何食物鏈通常不超過四五級？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>生產者固碳分解者釋碳回環境</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>牽動相關物種數量破壞平衡</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>能量逐級遞減不足支持</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>越高階可用能量越少</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>生產者大量減少對整個生態系的影響？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>牽動相關物種數量破壞平衡</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>多條交織更貼近真實複雜關係</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>能量來源減少各階層受衝擊</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>太陽經生產者沿食物鏈逐級傳遞且每級遞減</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>連鎖</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物8-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>植物</t>
+          <t>自己製造：像植物一樣能行光合作用自己製造養分的生物，稱為生產者</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>動物</t>
+          <t>攝食他物：不會自己製造養分，必須吃其他生物來獲取養分的生物稱為消費者</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>細菌真菌</t>
+          <t>分解遺體：像細菌和真菌這樣把動植物的遺體分解掉的生物，稱為分解者</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>陽光</t>
+          <t>陽光提供：生態系中所有能量最初都來自太陽的光，再由生產者轉換利用</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>鏈</t>
+          <t>傳遞路徑：能量會依照誰吃誰的順序，沿著食物鏈一級一級傳遞下去</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>遞減</t>
+          <t>逐漸減少：能量每往上傳一個階層，就會有一部分變成熱散失，所以越往上越少</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>可以循環：像碳這類物質可以在生物與環境間反覆利用，不會像能量一樣消失</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>網</t>
+          <t>交錯連結：許多條食物鏈彼此交叉連接在一起，就形成了複雜的食物網</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>生產者</t>
+          <t>生產者：植物能行光合作用自行製造養分，是生態系中的生產者，也是食物鏈的基礎</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>消費者</t>
+          <t>消費者：動物無法自行製造養分，必須攝食其他生物來獲取能量，屬於生態系中的消費者</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>能量流向</t>
+          <t>能量流向：食物鏈的箭頭代表能量傳遞的方向，是指向吃掉別人的那個取食者</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>遞減</t>
+          <t>逐級遞減：能量每經過一個階層就會流失一部分，所以階層越高能得到的能量越少</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>回歸環境：分解者把生物遺體分解成簡單物質，讓養分能再回到環境中被利用</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>環境</t>
+          <t>兩大部分：生態系不只包含各種生物，還包含陽光、空氣、水、土壤等非生物環境</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>頂端</t>
+          <t>位居頂端：鷹在這條食物鏈中吃兔子，位置最高，屬於高階消費者</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>不循環</t>
+          <t>只進不回：能量從太陽經生產者流向消費者後，大多以熱散失，不會再流回原處</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>物質循環</t>
+          <t>反覆利用：碳能在生物體、空氣與環境之間不斷轉換流動，屬於物質循環的一種</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>製養</t>
+          <t>自行製造：植物利用陽光、水和二氧化碳進行光合作用，自己製造養分與能量</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>遞減</t>
+          <t>遞減：能量沿著食物鏈傳遞時，大部分會以熱能等形式散失，只有一小部分（通常約十分之一）會傳遞到下一營養級</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：分解者負責把動植物遺體和廢物分解成簡單物質歸還環境，若缺少分解者，物質就無法循環利用，生態系會逐漸失衡</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>流動</t>
+          <t>逐級傳遞：能量從太陽進入生產者後，沿著食物鏈往上傳給消費者，每往上一層就少一些</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>性質不同：能量傳遞時大多變成熱散失到空氣中無法收回，但物質能被分解者分解後重複利用</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>關鍵</t>
+          <t>橋樑角色：分解者把死掉的生物分解成簡單物質，讓養分回到環境中供生產者再次利用</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>食物網</t>
+          <t>更貼近真實：自然界中一種生物常吃很多種食物，食物網能呈現這種複雜交錯的真實關係</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>連鎖</t>
+          <t>連鎖反應：某一種生物數量驟減，會讓吃牠的生物和牠吃的生物數量都跟著改變</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>能量塔</t>
+          <t>逐層縮小：越往食物鏈上層，能利用的能量越少，所以能量塔的形狀是下面寬、上面窄</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>碳循環</t>
+          <t>角色分工：生產者行光合作用把碳固定在體內，分解者則把碳釋放回環境形成循環</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>持續運作：陽光不斷提供能量、物質不斷循環利用，這樣生態系才能穩定地持續運作</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：能量沿食物鏈往上傳遞時每一級都大量流失，傳到第四、五級時剩下的能量已經很少，不足以再支持更高一級的生物族群生存，所以食物鏈通常不會太長</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>連鎖</t>
+          <t>連鎖：生產者是整個食物鏈能量的最初來源，一旦生產者大量減少，直接依賴它的消費者食物不足，會一層層向上影響到整個生態系的各個階層</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物8-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-2_三種難度測驗卷.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>生產者</t>
+          <t>物質無法循環</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>逐級遞減</t>
+          <t>非生物環境</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>太陽</t>
+          <t>單向</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>物質無法循環</t>
+          <t>食物鏈</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>食物鏈</t>
+          <t>光合作用</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>太陽</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>生產者</t>
+          <t>分解者</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>取食者</t>
+          <t>太陽</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>分解者</t>
+          <t>食物鏈</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1284,17 +1284,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>物質無法循環</t>
+          <t>生產者</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>能</t>
+          <t>食物鏈</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>食物鏈</t>
+          <t>消費者</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>分解者</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>太陽</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>生產者</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>太陽</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>消費者</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
